--- a/nursing/フォーマット/06_事故苦情ヒヤリ様式/06_研修受講記録.xlsx
+++ b/nursing/フォーマット/06_事故苦情ヒヤリ様式/06_研修受講記録.xlsx
@@ -26,40 +26,41 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
+      <name val="Meiryo"/>
       <b val="1"/>
-      <color rgb="000E7490"/>
-      <sz val="13"/>
+      <color rgb="00163A2B"/>
+      <sz val="16"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <b val="1"/>
+      <name val="Meiryo"/>
+      <color rgb="005C665C"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
+      <name val="Meiryo"/>
+      <color rgb="00283129"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
       <i val="1"/>
-      <color rgb="006B7280"/>
+      <color rgb="005C665C"/>
       <sz val="9"/>
     </font>
-    <font>
-      <name val="Meiryo UI"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Meiryo UI"/>
-      <b val="1"/>
-      <color rgb="00DC2626"/>
-      <sz val="8"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -68,16 +69,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000E7490"/>
+        <fgColor rgb="001F4D3A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8FAFC"/>
+        <fgColor rgb="00F6EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9854A"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -86,32 +92,72 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <bottom style="medium">
+        <color rgb="00A9854A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00A9854A"/>
+      </left>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A9854A"/>
+      </left>
+      <right style="thin">
+        <color rgb="00A9854A"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A9854A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A9854A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00DAD3C2"/>
+      </left>
+      <right style="thin">
+        <color rgb="00DAD3C2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DAD3C2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DAD3C2"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -476,422 +522,236 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>研修受講記録</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
+    <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>事業所名：</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　年度</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+          <t>虐待防止・身体拘束適正化・感染症・BCP等の法定研修は年間計画に基づき実施・記録</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>年間で実施が求められる主な研修（障害福祉）</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="8" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>虐待防止研修（年1回以上）／身体拘束適正化研修（年1回以上）／感染症・食中毒予防研修（年1回以上）／BCP研修（年1回以上）／衛生・安全／個人情報保護　※委員会の設置・指針整備とセットで義務</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>実施日</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>研修名・テーマ</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>主催・講師</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>研修テーマ</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>形式</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>参加者氏名</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>講師・主催</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>参加者数</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>内容（要旨）</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>確認者</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>2026/4/10</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>虐待防止・権利擁護研修</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>管理者（社内）</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>集合</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>全職員</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>虐待の定義・通報義務・日常的な権利擁護の重要性を確認。事例をもとにグループ討議実施。</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>山田 管理者</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>2026/5/20</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>個人情報保護研修</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>管理者（社内）</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>集合</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>全職員</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>個人情報保護法の改正点・要配慮個人情報の取扱い・漏洩時の対応を学習。</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>山田 管理者</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>2026/6/15</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>感染症対策研修</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>管理者（社内）</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>集合</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>全職員</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>標準予防策・手指衛生・PPEの正しい使用方法を確認。</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>山田 管理者</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="5" t="inlineStr"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="inlineStr"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="5" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="5" t="inlineStr"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="inlineStr"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="inlineStr"/>
-      <c r="F8" s="5" t="inlineStr"/>
-      <c r="G8" s="5" t="inlineStr"/>
-      <c r="H8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="5" t="inlineStr"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="inlineStr"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="inlineStr"/>
-      <c r="F9" s="5" t="inlineStr"/>
-      <c r="G9" s="5" t="inlineStr"/>
-      <c r="H9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="5" t="inlineStr"/>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="5" t="inlineStr"/>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="5" t="inlineStr"/>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="5" t="inlineStr"/>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="5" t="inlineStr"/>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="inlineStr"/>
-      <c r="F13" s="5" t="inlineStr"/>
-      <c r="G13" s="5" t="inlineStr"/>
-      <c r="H13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="5" t="inlineStr"/>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="inlineStr"/>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="inlineStr"/>
-      <c r="F14" s="5" t="inlineStr"/>
-      <c r="G14" s="5" t="inlineStr"/>
-      <c r="H14" s="5" t="inlineStr"/>
-    </row>
-    <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="5" t="inlineStr"/>
-      <c r="B15" s="5" t="inlineStr"/>
-      <c r="C15" s="5" t="inlineStr"/>
-      <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="5" t="inlineStr"/>
-      <c r="G15" s="5" t="inlineStr"/>
-      <c r="H15" s="5" t="inlineStr"/>
-    </row>
-    <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="5" t="inlineStr"/>
-      <c r="B16" s="5" t="inlineStr"/>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-    </row>
-    <row r="17" ht="40" customHeight="1">
-      <c r="A17" s="5" t="inlineStr"/>
-      <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-    </row>
-    <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="5" t="inlineStr"/>
-      <c r="B18" s="5" t="inlineStr"/>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19" ht="40" customHeight="1">
-      <c r="A19" s="5" t="inlineStr"/>
-      <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="5" t="inlineStr"/>
-      <c r="D19" s="5" t="inlineStr"/>
-      <c r="E19" s="5" t="inlineStr"/>
-      <c r="F19" s="5" t="inlineStr"/>
-      <c r="G19" s="5" t="inlineStr"/>
-      <c r="H19" s="5" t="inlineStr"/>
-    </row>
-    <row r="20" ht="40" customHeight="1">
-      <c r="A20" s="5" t="inlineStr"/>
-      <c r="B20" s="5" t="inlineStr"/>
-      <c r="C20" s="5" t="inlineStr"/>
-      <c r="D20" s="5" t="inlineStr"/>
-      <c r="E20" s="5" t="inlineStr"/>
-      <c r="F20" s="5" t="inlineStr"/>
-      <c r="G20" s="5" t="inlineStr"/>
-      <c r="H20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21" ht="40" customHeight="1">
-      <c r="A21" s="5" t="inlineStr"/>
-      <c r="B21" s="5" t="inlineStr"/>
-      <c r="C21" s="5" t="inlineStr"/>
-      <c r="D21" s="5" t="inlineStr"/>
-      <c r="E21" s="5" t="inlineStr"/>
-      <c r="F21" s="5" t="inlineStr"/>
-      <c r="G21" s="5" t="inlineStr"/>
-      <c r="H21" s="5" t="inlineStr"/>
-    </row>
-    <row r="22" ht="40" customHeight="1">
-      <c r="A22" s="5" t="inlineStr"/>
-      <c r="B22" s="5" t="inlineStr"/>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-    </row>
-    <row r="23" ht="40" customHeight="1">
-      <c r="A23" s="5" t="inlineStr"/>
-      <c r="B23" s="5" t="inlineStr"/>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-    </row>
-    <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="5" t="inlineStr"/>
-      <c r="B24" s="5" t="inlineStr"/>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-    </row>
-    <row r="25" ht="40" customHeight="1">
-      <c r="A25" s="5" t="inlineStr"/>
-      <c r="B25" s="5" t="inlineStr"/>
-      <c r="C25" s="5" t="inlineStr"/>
-      <c r="D25" s="5" t="inlineStr"/>
-      <c r="E25" s="5" t="inlineStr"/>
-      <c r="F25" s="5" t="inlineStr"/>
-      <c r="G25" s="5" t="inlineStr"/>
-      <c r="H25" s="5" t="inlineStr"/>
-    </row>
-    <row r="26" ht="40" customHeight="1">
-      <c r="A26" s="5" t="inlineStr"/>
-      <c r="B26" s="5" t="inlineStr"/>
-      <c r="C26" s="5" t="inlineStr"/>
-      <c r="D26" s="5" t="inlineStr"/>
-      <c r="E26" s="5" t="inlineStr"/>
-      <c r="F26" s="5" t="inlineStr"/>
-      <c r="G26" s="5" t="inlineStr"/>
-      <c r="H26" s="5" t="inlineStr"/>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>【最低限年1回実施が必要な研修】虐待防止研修 / 個人情報保護研修 / 感染症対策研修 / 身体拘束防止研修</t>
-        </is>
-      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>記録・資料の保管</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>（例）2025/05/20</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>高齢者・障害者虐待防止</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>内部</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>管理者</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>資料・出席簿あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="10" t="n"/>
+      <c r="B8" s="10" t="n"/>
+      <c r="C8" s="10" t="n"/>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="10" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="10" t="n"/>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="10" t="n"/>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="10" t="n"/>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="10" t="n"/>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="10" t="n"/>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="10" t="n"/>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="10" t="n"/>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="10" t="n"/>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="10" t="n"/>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>※ 未受講者には個別にフォロー（資料回覧・後日視聴）。出席簿・使用資料・理解度確認を一緒に保管。</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A1:H1"/>
+  <mergeCells count="5">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A4:F4"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>